--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_67_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_67_IN_Piura.xlsx
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>49.35</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C11" s="30">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>48.53</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>2.12</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1916,11 +1916,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>13.1838</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1941,11 +1941,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>12.9045</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>97.88</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>0.2793</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>2.12</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>13.1865</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2249,6 +2249,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2333,6 +2334,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2377,6 +2379,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="144" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2761,11 +2764,11 @@
       </c>
       <c r="B17" s="32">
         <f>SUM(B10:B16)</f>
-        <v/>
+        <v>273.96</v>
       </c>
       <c r="C17" s="23">
         <f>SUM(C10:C16)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -2775,19 +2778,19 @@
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17">
         <f>ROUND(AVERAGE(F10:F16),2)</f>
-        <v/>
+        <v>29.26</v>
       </c>
       <c r="G17" s="22">
         <f>ROUND(AVERAGE(G10:G16),4)</f>
-        <v/>
+        <v>0.5792</v>
       </c>
       <c r="H17" s="23">
         <f>ROUND(AVERAGE(H10:H16),2)</f>
-        <v/>
+        <v>90.14</v>
       </c>
       <c r="I17" s="23">
         <f>ROUND(AVERAGE(I10:I16),2)</f>
-        <v/>
+        <v>14.61</v>
       </c>
     </row>
     <row r="18"/>
